--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1066,13 +1066,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46003.0)</f>
         <v>46003</v>
       </c>
-      <c r="B13" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.65)</f>
+        <v>248.65</v>
       </c>
       <c r="C13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="D13" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1075,52 +1075,52 @@
         <v>18.08363636</v>
       </c>
       <c r="D13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="E13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="F13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="G13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="H13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="I13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="J13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="L13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="M13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="N13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="O13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="P13" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1066,61 +1066,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46003.0)</f>
         <v>46003</v>
       </c>
-      <c r="B13" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.65)</f>
+        <v>248.65</v>
       </c>
       <c r="C13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="D13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="E13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="F13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="G13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="H13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="I13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="J13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="L13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="M13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="N13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="O13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
+        <v>18.08363636</v>
       </c>
       <c r="P13" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
@@ -1132,61 +1132,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46004.0)</f>
         <v>46004</v>
       </c>
-      <c r="B14" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),385.85)</f>
+        <v>385.85</v>
       </c>
       <c r="C14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="D14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="E14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="F14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="G14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="H14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="I14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="J14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="L14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="M14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="N14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="O14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
+        <v>28.06181818</v>
       </c>
       <c r="P14" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1198,61 +1198,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46005.0)</f>
         <v>46005</v>
       </c>
-      <c r="B15" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.25)</f>
+        <v>229.25</v>
       </c>
       <c r="C15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="D15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="E15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="F15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="G15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="H15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="I15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="J15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="L15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="M15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="N15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="O15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
+        <v>16.67272727</v>
       </c>
       <c r="P15" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1264,61 +1264,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46006.0)</f>
         <v>46006</v>
       </c>
-      <c r="B16" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.6)</f>
+        <v>178.6</v>
       </c>
       <c r="C16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="D16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="E16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="F16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="G16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="H16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="I16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="J16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="L16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="M16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="N16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="O16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
+        <v>12.98909091</v>
       </c>
       <c r="P16" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1330,61 +1330,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46007.0)</f>
         <v>46007</v>
       </c>
-      <c r="B17" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),171.1)</f>
+        <v>171.1</v>
       </c>
       <c r="C17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="D17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="E17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="F17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="G17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="H17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="I17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="J17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="L17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="M17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="N17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="O17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
+        <v>12.44363636</v>
       </c>
       <c r="P17" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1396,61 +1396,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46008.0)</f>
         <v>46008</v>
       </c>
-      <c r="B18" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.65)</f>
+        <v>145.65</v>
       </c>
       <c r="C18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="D18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="E18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="F18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="G18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="H18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="I18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="J18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="L18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="M18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="N18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="O18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="P18" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1396,61 +1396,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46008.0)</f>
         <v>46008</v>
       </c>
-      <c r="B18" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.65)</f>
+        <v>145.65</v>
       </c>
       <c r="C18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="D18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="E18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="F18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="G18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="H18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="I18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="J18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="L18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="M18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="N18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="O18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
+        <v>10.59272727</v>
       </c>
       <c r="P18" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
@@ -1462,61 +1462,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46009.0)</f>
         <v>46009</v>
       </c>
-      <c r="B19" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.35)</f>
+        <v>198.35</v>
       </c>
       <c r="C19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="D19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="E19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="F19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="G19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="H19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="I19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="J19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="L19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="M19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="N19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="O19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="P19" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1462,61 +1462,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46009.0)</f>
         <v>46009</v>
       </c>
-      <c r="B19" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.35)</f>
+        <v>198.35</v>
       </c>
       <c r="C19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="D19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="E19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="F19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="G19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="H19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="I19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="J19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="L19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="M19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="N19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="O19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
+        <v>14.42545455</v>
       </c>
       <c r="P19" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1528,61 +1528,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46010.0)</f>
         <v>46010</v>
       </c>
-      <c r="B20" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),123.5)</f>
+        <v>123.5</v>
       </c>
       <c r="C20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="D20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="E20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="F20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="G20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="H20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="I20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="J20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="L20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="M20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="N20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="O20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
+        <v>8.981818182</v>
       </c>
       <c r="P20" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1594,61 +1594,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46011.0)</f>
         <v>46011</v>
       </c>
-      <c r="B21" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.55)</f>
+        <v>309.55</v>
       </c>
       <c r="C21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="D21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="E21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="F21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="G21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="H21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="I21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="J21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="L21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="M21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="N21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="O21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
+        <v>22.51272727</v>
       </c>
       <c r="P21" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
@@ -1660,61 +1660,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46012.0)</f>
         <v>46012</v>
       </c>
-      <c r="B22" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),272.5)</f>
+        <v>272.5</v>
       </c>
       <c r="C22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="D22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="E22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="F22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="G22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="H22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="I22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="J22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="L22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="M22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="N22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="O22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
+        <v>19.81818182</v>
       </c>
       <c r="P22" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1726,65 +1726,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46013.0)</f>
         <v>46013</v>
       </c>
-      <c r="B23" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.45)</f>
+        <v>211.45</v>
       </c>
       <c r="C23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
       </c>
       <c r="D23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
       </c>
       <c r="E23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
       </c>
       <c r="F23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
       </c>
       <c r="G23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
       </c>
       <c r="H23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
       </c>
       <c r="I23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
       </c>
       <c r="J23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
       </c>
       <c r="L23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
       </c>
       <c r="M23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="N23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
+      </c>
+      <c r="N23" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="O23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
+        <v>16.916</v>
       </c>
       <c r="P23" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -1840,17 +1840,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="N24" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
+      </c>
+      <c r="O24" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="P24" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1910,13 +1910,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="O25" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="P25" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -1976,13 +1976,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="O26" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="P26" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -2042,13 +2042,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="O27" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="P27" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -2108,13 +2108,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="O28" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="P28" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -2174,13 +2174,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="O29" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="P29" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -2240,13 +2240,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="O30" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="P30" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -2306,13 +2306,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="O31" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="P31" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -2372,13 +2372,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="O32" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="P32" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1792,53 +1792,53 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46014.0)</f>
         <v>46014</v>
       </c>
-      <c r="B24" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.95)</f>
+        <v>110.95</v>
       </c>
       <c r="C24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
+        <v>11.095</v>
       </c>
       <c r="D24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
+        <v>11.095</v>
       </c>
       <c r="E24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
+        <v>11.095</v>
       </c>
       <c r="F24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
+        <v>11.095</v>
+      </c>
+      <c r="G24" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="H24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
+        <v>11.095</v>
       </c>
       <c r="I24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
+        <v>11.095</v>
       </c>
       <c r="J24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
+        <v>11.095</v>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
+        <v>11.095</v>
       </c>
       <c r="L24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
+        <v>11.095</v>
       </c>
       <c r="M24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
+        <v>11.095</v>
       </c>
       <c r="N24" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
@@ -1849,8 +1849,8 @@
         <v>x</v>
       </c>
       <c r="P24" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -1924,57 +1924,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46016.0)</f>
         <v>46016</v>
       </c>
-      <c r="B26" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="C26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="D26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="E26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="F26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="G26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="H26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="I26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="J26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="L26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="M26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="N26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
+        <v>7.04</v>
       </c>
       <c r="O26" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1990,57 +1990,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46017.0)</f>
         <v>46017</v>
       </c>
-      <c r="B27" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),192.75)</f>
+        <v>192.75</v>
       </c>
       <c r="C27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="D27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="E27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="F27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="G27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="H27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="I27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="J27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="L27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="M27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="N27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
+        <v>15.42</v>
       </c>
       <c r="O27" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1858,9 +1858,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46015.0)</f>
         <v>46015</v>
       </c>
-      <c r="B25" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="C25" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2056,57 +2056,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46018.0)</f>
         <v>46018</v>
       </c>
-      <c r="B28" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.2)</f>
+        <v>262.2</v>
       </c>
       <c r="C28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="D28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="E28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="F28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="G28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="H28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="I28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="J28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="L28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="M28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="N28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
+        <v>20.976</v>
       </c>
       <c r="O28" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -2122,57 +2122,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46019.0)</f>
         <v>46019</v>
       </c>
-      <c r="B29" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B29" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.15)</f>
+        <v>348.15</v>
       </c>
       <c r="C29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="D29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="E29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="F29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="G29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="H29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="I29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="J29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="L29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="M29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="N29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
+        <v>27.852</v>
       </c>
       <c r="O29" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -2188,65 +2188,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46020.0)</f>
         <v>46020</v>
       </c>
-      <c r="B30" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B30" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),288.2)</f>
+        <v>288.2</v>
       </c>
       <c r="C30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
+        <v>25.61777778</v>
       </c>
       <c r="D30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
+        <v>25.61777778</v>
       </c>
       <c r="E30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
+        <v>25.61777778</v>
       </c>
       <c r="F30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
+        <v>25.61777778</v>
       </c>
       <c r="G30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
+        <v>25.61777778</v>
+      </c>
+      <c r="H30" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
+        <v>25.61777778</v>
       </c>
       <c r="J30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
+        <v>25.61777778</v>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
+        <v>25.61777778</v>
       </c>
       <c r="L30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
+        <v>25.61777778</v>
       </c>
       <c r="M30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
+        <v>25.61777778</v>
       </c>
       <c r="N30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
+        <v>25.61777778</v>
       </c>
       <c r="O30" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="P30" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -2278,9 +2278,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H31" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I31" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2311,8 +2311,8 @@
         <v>x</v>
       </c>
       <c r="P31" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="32">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -2193,60 +2193,60 @@
         <v>288.2</v>
       </c>
       <c r="C30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
-        <v>25.61777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
+        <v>28.82</v>
       </c>
       <c r="D30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
-        <v>25.61777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
+        <v>28.82</v>
       </c>
       <c r="E30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
-        <v>25.61777778</v>
-      </c>
-      <c r="F30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
-        <v>25.61777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
+        <v>28.82</v>
+      </c>
+      <c r="F30" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="G30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
-        <v>25.61777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
+        <v>28.82</v>
       </c>
       <c r="H30" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="I30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
-        <v>25.61777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
+        <v>28.82</v>
       </c>
       <c r="J30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
-        <v>25.61777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
+        <v>28.82</v>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
-        <v>25.61777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
+        <v>28.82</v>
       </c>
       <c r="L30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
-        <v>25.61777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
+        <v>28.82</v>
       </c>
       <c r="M30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
-        <v>25.61777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
+        <v>28.82</v>
       </c>
       <c r="N30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.617777777777775)</f>
-        <v>25.61777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
+        <v>28.82</v>
       </c>
       <c r="O30" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="P30" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -2254,65 +2254,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46021.0)</f>
         <v>46021</v>
       </c>
-      <c r="B31" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B31" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.55)</f>
+        <v>218.55</v>
       </c>
       <c r="C31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
+        <v>21.855</v>
       </c>
       <c r="D31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
+        <v>21.855</v>
       </c>
       <c r="E31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
+        <v>21.855</v>
+      </c>
+      <c r="F31" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="G31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
+        <v>21.855</v>
       </c>
       <c r="H31" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="I31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
+        <v>21.855</v>
       </c>
       <c r="J31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
+        <v>21.855</v>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
+        <v>21.855</v>
       </c>
       <c r="L31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
+        <v>21.855</v>
       </c>
       <c r="M31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
+        <v>21.855</v>
       </c>
       <c r="N31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
+        <v>21.855</v>
       </c>
       <c r="O31" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="P31" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -2320,9 +2320,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46022.0)</f>
         <v>46022</v>
       </c>
-      <c r="B32" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B32" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="C32" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -271,7 +271,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1AfOc_5lC7c-UIkJPwOl_FRj1ZV9c_e0k-sww0ubD6zA/edit?gid=1929580256#gid=1929580256"",""Dezembro!A1:P32"")"),"Data")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1POsjPVrSf7cI9l6RV9YTekpgPrIXrtJUSYTfH7IdCBw/edit?gid=1929580256#gid=1929580256"",""Janeiro!A1:P32"")"),"Data")</f>
         <v>Data</v>
       </c>
       <c r="B1" s="1" t="str">
@@ -327,8 +327,8 @@
         <v>Naiane</v>
       </c>
       <c r="O1" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Raisa")</f>
-        <v>Raisa</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Coluna 15")</f>
+        <v>Coluna 15</v>
       </c>
       <c r="P1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Colaboradores")</f>
@@ -337,65 +337,62 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45992.0)</f>
-        <v>45992</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
+        <v>46023</v>
       </c>
       <c r="B2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),356.0)</f>
-        <v>356</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.9)</f>
+        <v>258.9</v>
       </c>
       <c r="C2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
       </c>
       <c r="D2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
       </c>
       <c r="E2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
       </c>
       <c r="F2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
-      </c>
-      <c r="G2" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
+      </c>
+      <c r="G2" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
       </c>
       <c r="H2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
       </c>
       <c r="I2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
       </c>
       <c r="J2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
       </c>
       <c r="L2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
       </c>
       <c r="M2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
       </c>
       <c r="N2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
-      </c>
-      <c r="O2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.48)</f>
-        <v>28.48</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.711999999999996)</f>
+        <v>20.712</v>
+      </c>
+      <c r="O2" s="1"/>
       <c r="P2" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -403,65 +400,62 @@
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45993.0)</f>
-        <v>45993</v>
-      </c>
-      <c r="B3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),232.35)</f>
-        <v>232.35</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46024.0)</f>
+        <v>46024</v>
+      </c>
+      <c r="B3" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
-      </c>
-      <c r="O3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.588)</f>
-        <v>18.588</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="1"/>
       <c r="P3" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -469,65 +463,62 @@
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45994.0)</f>
-        <v>45994</v>
-      </c>
-      <c r="B4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.38)</f>
-        <v>283.38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46025.0)</f>
+        <v>46025</v>
+      </c>
+      <c r="B4" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
-      </c>
-      <c r="G4" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
-      </c>
-      <c r="O4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.6704)</f>
-        <v>22.6704</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="1"/>
       <c r="P4" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -535,65 +526,62 @@
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45995.0)</f>
-        <v>45995</v>
-      </c>
-      <c r="B5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.6)</f>
-        <v>366.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46026.0)</f>
+        <v>46026</v>
+      </c>
+      <c r="B5" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
-      </c>
-      <c r="G5" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
-      </c>
-      <c r="O5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.328000000000003)</f>
-        <v>29.328</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="1"/>
       <c r="P5" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -601,65 +589,62 @@
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45996.0)</f>
-        <v>45996</v>
-      </c>
-      <c r="B6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.2)</f>
-        <v>265.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46027.0)</f>
+        <v>46027</v>
+      </c>
+      <c r="B6" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
-      </c>
-      <c r="G6" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
-      </c>
-      <c r="O6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.216)</f>
-        <v>21.216</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="1"/>
       <c r="P6" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -667,65 +652,62 @@
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45997.0)</f>
-        <v>45997</v>
-      </c>
-      <c r="B7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.35)</f>
-        <v>386.35</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46028.0)</f>
+        <v>46028</v>
+      </c>
+      <c r="B7" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
-      </c>
-      <c r="G7" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
-      </c>
-      <c r="O7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.908000000000005)</f>
-        <v>30.908</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="1"/>
       <c r="P7" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -733,263 +715,251 @@
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45998.0)</f>
-        <v>45998</v>
-      </c>
-      <c r="B8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.0)</f>
-        <v>286</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46029.0)</f>
+        <v>46029</v>
+      </c>
+      <c r="B8" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.422222222222224)</f>
-        <v>25.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.422222222222224)</f>
-        <v>25.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.422222222222224)</f>
-        <v>25.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.422222222222224)</f>
-        <v>25.42222222</v>
-      </c>
-      <c r="G8" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
-      <c r="H8" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.422222222222224)</f>
-        <v>25.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.422222222222224)</f>
-        <v>25.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.422222222222224)</f>
-        <v>25.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.422222222222224)</f>
-        <v>25.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.422222222222224)</f>
-        <v>25.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.422222222222224)</f>
-        <v>25.42222222</v>
-      </c>
-      <c r="O8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.422222222222224)</f>
-        <v>25.42222222</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="1"/>
       <c r="P8" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45999.0)</f>
-        <v>45999</v>
-      </c>
-      <c r="B9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),257.55)</f>
-        <v>257.55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46030.0)</f>
+        <v>46030</v>
+      </c>
+      <c r="B9" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.893333333333334)</f>
-        <v>22.89333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.893333333333334)</f>
-        <v>22.89333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.893333333333334)</f>
-        <v>22.89333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.893333333333334)</f>
-        <v>22.89333333</v>
-      </c>
-      <c r="G9" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
-      <c r="H9" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.893333333333334)</f>
-        <v>22.89333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.893333333333334)</f>
-        <v>22.89333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.893333333333334)</f>
-        <v>22.89333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.893333333333334)</f>
-        <v>22.89333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.893333333333334)</f>
-        <v>22.89333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.893333333333334)</f>
-        <v>22.89333333</v>
-      </c>
-      <c r="O9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.893333333333334)</f>
-        <v>22.89333333</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="1"/>
       <c r="P9" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46000.0)</f>
-        <v>46000</v>
-      </c>
-      <c r="B10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),317.2)</f>
-        <v>317.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46031.0)</f>
+        <v>46031</v>
+      </c>
+      <c r="B10" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.19555555555555)</f>
-        <v>28.19555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.19555555555555)</f>
-        <v>28.19555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.19555555555555)</f>
-        <v>28.19555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.19555555555555)</f>
-        <v>28.19555556</v>
-      </c>
-      <c r="G10" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
-      <c r="H10" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.19555555555555)</f>
-        <v>28.19555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.19555555555555)</f>
-        <v>28.19555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.19555555555555)</f>
-        <v>28.19555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.19555555555555)</f>
-        <v>28.19555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.19555555555555)</f>
-        <v>28.19555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.19555555555555)</f>
-        <v>28.19555556</v>
-      </c>
-      <c r="O10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.19555555555555)</f>
-        <v>28.19555556</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="1"/>
       <c r="P10" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46001.0)</f>
-        <v>46001</v>
-      </c>
-      <c r="B11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283.25)</f>
-        <v>283.25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
+        <v>46032</v>
+      </c>
+      <c r="B11" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
-      </c>
-      <c r="G11" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
-      </c>
-      <c r="O11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.66)</f>
-        <v>22.66</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="1"/>
       <c r="P11" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -997,791 +967,755 @@
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46002.0)</f>
-        <v>46002</v>
-      </c>
-      <c r="B12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),221.0)</f>
-        <v>221</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46033.0)</f>
+        <v>46033</v>
+      </c>
+      <c r="B12" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
-      </c>
-      <c r="O12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.07272727272727)</f>
-        <v>16.07272727</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="1"/>
       <c r="P12" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46003.0)</f>
-        <v>46003</v>
-      </c>
-      <c r="B13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.65)</f>
-        <v>248.65</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
+        <v>46034</v>
+      </c>
+      <c r="B13" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
-      </c>
-      <c r="O13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.083636363636366)</f>
-        <v>18.08363636</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="1"/>
       <c r="P13" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46004.0)</f>
-        <v>46004</v>
-      </c>
-      <c r="B14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),385.85)</f>
-        <v>385.85</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46035.0)</f>
+        <v>46035</v>
+      </c>
+      <c r="B14" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
-      </c>
-      <c r="O14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.061818181818182)</f>
-        <v>28.06181818</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="1"/>
       <c r="P14" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46005.0)</f>
-        <v>46005</v>
-      </c>
-      <c r="B15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),229.25)</f>
-        <v>229.25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46036.0)</f>
+        <v>46036</v>
+      </c>
+      <c r="B15" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
-      </c>
-      <c r="O15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.672727272727272)</f>
-        <v>16.67272727</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="1"/>
       <c r="P15" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46006.0)</f>
-        <v>46006</v>
-      </c>
-      <c r="B16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.6)</f>
-        <v>178.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46037.0)</f>
+        <v>46037</v>
+      </c>
+      <c r="B16" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
-      </c>
-      <c r="O16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.989090909090908)</f>
-        <v>12.98909091</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="1"/>
       <c r="P16" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46007.0)</f>
-        <v>46007</v>
-      </c>
-      <c r="B17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),171.1)</f>
-        <v>171.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46038.0)</f>
+        <v>46038</v>
+      </c>
+      <c r="B17" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
-      </c>
-      <c r="O17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.443636363636363)</f>
-        <v>12.44363636</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="1"/>
       <c r="P17" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46008.0)</f>
-        <v>46008</v>
-      </c>
-      <c r="B18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145.65)</f>
-        <v>145.65</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46039.0)</f>
+        <v>46039</v>
+      </c>
+      <c r="B18" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
-      </c>
-      <c r="O18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.592727272727274)</f>
-        <v>10.59272727</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="1"/>
       <c r="P18" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46009.0)</f>
-        <v>46009</v>
-      </c>
-      <c r="B19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.35)</f>
-        <v>198.35</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46040.0)</f>
+        <v>46040</v>
+      </c>
+      <c r="B19" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
-      </c>
-      <c r="O19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.425454545454546)</f>
-        <v>14.42545455</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="1"/>
       <c r="P19" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46010.0)</f>
-        <v>46010</v>
-      </c>
-      <c r="B20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),123.5)</f>
-        <v>123.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46041.0)</f>
+        <v>46041</v>
+      </c>
+      <c r="B20" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
-      </c>
-      <c r="O20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.98181818181818)</f>
-        <v>8.981818182</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="1"/>
       <c r="P20" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46011.0)</f>
-        <v>46011</v>
-      </c>
-      <c r="B21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309.55)</f>
-        <v>309.55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
+        <v>46042</v>
+      </c>
+      <c r="B21" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
-      </c>
-      <c r="O21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.512727272727272)</f>
-        <v>22.51272727</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="1"/>
       <c r="P21" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46012.0)</f>
-        <v>46012</v>
-      </c>
-      <c r="B22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),272.5)</f>
-        <v>272.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
+        <v>46043</v>
+      </c>
+      <c r="B22" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
-      </c>
-      <c r="O22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.81818181818182)</f>
-        <v>19.81818182</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="1"/>
       <c r="P22" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46013.0)</f>
-        <v>46013</v>
-      </c>
-      <c r="B23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),211.45)</f>
-        <v>211.45</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46044.0)</f>
+        <v>46044</v>
+      </c>
+      <c r="B23" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
-      </c>
-      <c r="N23" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
-      <c r="O23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.916)</f>
-        <v>16.916</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="1"/>
       <c r="P23" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -1789,78 +1723,75 @@
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46014.0)</f>
-        <v>46014</v>
-      </c>
-      <c r="B24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.95)</f>
-        <v>110.95</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46045.0)</f>
+        <v>46045</v>
+      </c>
+      <c r="B24" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
-        <v>11.095</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
-        <v>11.095</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
-        <v>11.095</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
-        <v>11.095</v>
-      </c>
-      <c r="G24" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
-        <v>11.095</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
-        <v>11.095</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
-        <v>11.095</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
-        <v>11.095</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
-        <v>11.095</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.095)</f>
-        <v>11.095</v>
-      </c>
-      <c r="N24" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
-      <c r="O24" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="1"/>
       <c r="P24" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46015.0)</f>
-        <v>46015</v>
-      </c>
-      <c r="B25" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46046.0)</f>
+        <v>46046</v>
+      </c>
+      <c r="B25" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C25" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1910,10 +1841,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O25" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
+      <c r="O25" s="1"/>
       <c r="P25" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -1921,65 +1849,62 @@
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46016.0)</f>
-        <v>46016</v>
-      </c>
-      <c r="B26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46047.0)</f>
+        <v>46047</v>
+      </c>
+      <c r="B26" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.040000000000001)</f>
-        <v>7.04</v>
-      </c>
-      <c r="O26" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="1"/>
       <c r="P26" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -1987,65 +1912,62 @@
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46017.0)</f>
-        <v>46017</v>
-      </c>
-      <c r="B27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),192.75)</f>
-        <v>192.75</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46048.0)</f>
+        <v>46048</v>
+      </c>
+      <c r="B27" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.419999999999998)</f>
-        <v>15.42</v>
-      </c>
-      <c r="O27" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="1"/>
       <c r="P27" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -2053,65 +1975,62 @@
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46018.0)</f>
-        <v>46018</v>
-      </c>
-      <c r="B28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262.2)</f>
-        <v>262.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46049.0)</f>
+        <v>46049</v>
+      </c>
+      <c r="B28" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.976)</f>
-        <v>20.976</v>
-      </c>
-      <c r="O28" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="1"/>
       <c r="P28" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -2119,65 +2038,62 @@
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46019.0)</f>
-        <v>46019</v>
-      </c>
-      <c r="B29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),348.15)</f>
-        <v>348.15</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46050.0)</f>
+        <v>46050</v>
+      </c>
+      <c r="B29" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.851999999999997)</f>
-        <v>27.852</v>
-      </c>
-      <c r="O29" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="1"/>
       <c r="P29" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>
@@ -2185,144 +2101,138 @@
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46020.0)</f>
-        <v>46020</v>
-      </c>
-      <c r="B30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),288.2)</f>
-        <v>288.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46051.0)</f>
+        <v>46051</v>
+      </c>
+      <c r="B30" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
-        <v>28.82</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
-        <v>28.82</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
-        <v>28.82</v>
-      </c>
-      <c r="F30" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
-        <v>28.82</v>
-      </c>
-      <c r="H30" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
-        <v>28.82</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
-        <v>28.82</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
-        <v>28.82</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
-        <v>28.82</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
-        <v>28.82</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.82)</f>
-        <v>28.82</v>
-      </c>
-      <c r="O30" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="1"/>
       <c r="P30" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46021.0)</f>
-        <v>46021</v>
-      </c>
-      <c r="B31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.55)</f>
-        <v>218.55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46052.0)</f>
+        <v>46052</v>
+      </c>
+      <c r="B31" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
-        <v>21.855</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
-        <v>21.855</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="E31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
-        <v>21.855</v>
-      </c>
-      <c r="F31" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
-        <v>21.855</v>
-      </c>
-      <c r="H31" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
-        <v>21.855</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
-        <v>21.855</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
-        <v>21.855</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
-        <v>21.855</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
-        <v>21.855</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.855)</f>
-        <v>21.855</v>
-      </c>
-      <c r="O31" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="O31" s="1"/>
       <c r="P31" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46022.0)</f>
-        <v>46022</v>
-      </c>
-      <c r="B32" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46053.0)</f>
+        <v>46053</v>
+      </c>
+      <c r="B32" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C32" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2372,10 +2282,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O32" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
-      </c>
+      <c r="O32" s="1"/>
       <c r="P32" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
         <v>10</v>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -592,57 +592,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46027.0)</f>
         <v>46027</v>
       </c>
-      <c r="B6" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),226.95)</f>
+        <v>226.95</v>
       </c>
       <c r="C6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="D6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="E6" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="G6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="H6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="I6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="J6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="K6" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -592,57 +592,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46027.0)</f>
         <v>46027</v>
       </c>
-      <c r="B6" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),226.95)</f>
+        <v>226.95</v>
       </c>
       <c r="C6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="D6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="E6" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="G6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="H6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="I6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="J6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="K6" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
+        <v>22.695</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1">
@@ -655,57 +655,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46028.0)</f>
         <v>46028</v>
       </c>
-      <c r="B7" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.7)</f>
+        <v>217.7</v>
       </c>
       <c r="C7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
+        <v>21.77</v>
       </c>
       <c r="D7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
+        <v>21.77</v>
       </c>
       <c r="E7" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
+        <v>21.77</v>
       </c>
       <c r="G7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
+        <v>21.77</v>
       </c>
       <c r="H7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
+        <v>21.77</v>
       </c>
       <c r="I7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
+        <v>21.77</v>
       </c>
       <c r="J7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
+        <v>21.77</v>
       </c>
       <c r="K7" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
+        <v>21.77</v>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
+        <v>21.77</v>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
+        <v>21.77</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -718,57 +718,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46029.0)</f>
         <v>46029</v>
       </c>
-      <c r="B8" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),354.55)</f>
+        <v>354.55</v>
       </c>
       <c r="C8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
+        <v>35.455</v>
       </c>
       <c r="D8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
+        <v>35.455</v>
       </c>
       <c r="E8" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
+        <v>35.455</v>
       </c>
       <c r="G8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
+        <v>35.455</v>
       </c>
       <c r="H8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
+        <v>35.455</v>
       </c>
       <c r="I8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
+        <v>35.455</v>
       </c>
       <c r="J8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
+        <v>35.455</v>
       </c>
       <c r="K8" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="L8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
+        <v>35.455</v>
       </c>
       <c r="M8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
+        <v>35.455</v>
       </c>
       <c r="N8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
+        <v>35.455</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -781,57 +781,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46030.0)</f>
         <v>46030</v>
       </c>
-      <c r="B9" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.65)</f>
+        <v>265.65</v>
       </c>
       <c r="C9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
+        <v>26.565</v>
       </c>
       <c r="D9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
+        <v>26.565</v>
       </c>
       <c r="E9" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
+        <v>26.565</v>
       </c>
       <c r="G9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
+        <v>26.565</v>
       </c>
       <c r="H9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
+        <v>26.565</v>
       </c>
       <c r="I9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
+        <v>26.565</v>
       </c>
       <c r="J9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
+        <v>26.565</v>
       </c>
       <c r="K9" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="L9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
+        <v>26.565</v>
       </c>
       <c r="M9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
+        <v>26.565</v>
       </c>
       <c r="N9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
+        <v>26.565</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1">
@@ -880,9 +880,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="K10" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="L10" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -898,8 +898,8 @@
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="11">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -844,57 +844,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46031.0)</f>
         <v>46031</v>
       </c>
-      <c r="B10" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.7)</f>
+        <v>331.7</v>
       </c>
       <c r="C10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="D10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="E10" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="G10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="H10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="I10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="J10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="K10" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="L10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="M10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="N10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -844,57 +844,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46031.0)</f>
         <v>46031</v>
       </c>
-      <c r="B10" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.7)</f>
+        <v>331.7</v>
       </c>
       <c r="C10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="D10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="E10" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="G10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="H10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="I10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="J10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="K10" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="L10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="M10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="N10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
+        <v>33.17</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1">
@@ -907,57 +907,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
         <v>46032</v>
       </c>
-      <c r="B11" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),561.6)</f>
+        <v>561.6</v>
       </c>
       <c r="C11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
+        <v>49.92</v>
       </c>
       <c r="D11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
+        <v>49.92</v>
       </c>
       <c r="E11" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
+        <v>49.92</v>
       </c>
       <c r="G11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
+        <v>49.92</v>
       </c>
       <c r="H11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
+        <v>49.92</v>
       </c>
       <c r="I11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
+        <v>49.92</v>
       </c>
       <c r="J11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
+        <v>49.92</v>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
+        <v>49.92</v>
       </c>
       <c r="L11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
+        <v>49.92</v>
       </c>
       <c r="M11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
+        <v>49.92</v>
       </c>
       <c r="N11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
+        <v>49.92</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -970,57 +970,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46033.0)</f>
         <v>46033</v>
       </c>
-      <c r="B12" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),510.55)</f>
+        <v>510.55</v>
       </c>
       <c r="C12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
+        <v>45.38222222</v>
       </c>
       <c r="D12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
+        <v>45.38222222</v>
       </c>
       <c r="E12" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
+        <v>45.38222222</v>
       </c>
       <c r="G12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
+        <v>45.38222222</v>
       </c>
       <c r="H12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
+        <v>45.38222222</v>
       </c>
       <c r="I12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
+        <v>45.38222222</v>
       </c>
       <c r="J12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
+        <v>45.38222222</v>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
+        <v>45.38222222</v>
       </c>
       <c r="L12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
+        <v>45.38222222</v>
       </c>
       <c r="M12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
+        <v>45.38222222</v>
       </c>
       <c r="N12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
+        <v>45.38222222</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1033,57 +1033,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
         <v>46034</v>
       </c>
-      <c r="B13" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),239.8)</f>
+        <v>239.8</v>
       </c>
       <c r="C13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
+        <v>21.31555556</v>
       </c>
       <c r="D13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
+        <v>21.31555556</v>
       </c>
       <c r="E13" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
+        <v>21.31555556</v>
       </c>
       <c r="G13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
+        <v>21.31555556</v>
       </c>
       <c r="H13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
+        <v>21.31555556</v>
       </c>
       <c r="I13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
+        <v>21.31555556</v>
       </c>
       <c r="J13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
+        <v>21.31555556</v>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
+        <v>21.31555556</v>
       </c>
       <c r="L13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
+        <v>21.31555556</v>
       </c>
       <c r="M13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
+        <v>21.31555556</v>
       </c>
       <c r="N13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
+        <v>21.31555556</v>
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="1">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -66,6 +66,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1096,57 +1100,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46035.0)</f>
         <v>46035</v>
       </c>
-      <c r="B14" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),188.9)</f>
+        <v>188.9</v>
       </c>
       <c r="C14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
+        <v>16.79111111</v>
       </c>
       <c r="D14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
+        <v>16.79111111</v>
       </c>
       <c r="E14" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
+        <v>16.79111111</v>
       </c>
       <c r="G14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
+        <v>16.79111111</v>
       </c>
       <c r="H14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
+        <v>16.79111111</v>
       </c>
       <c r="I14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
+        <v>16.79111111</v>
       </c>
       <c r="J14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
+        <v>16.79111111</v>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
+        <v>16.79111111</v>
       </c>
       <c r="L14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
+        <v>16.79111111</v>
       </c>
       <c r="M14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
+        <v>16.79111111</v>
       </c>
       <c r="N14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
+        <v>16.79111111</v>
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1163,57 +1163,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46036.0)</f>
         <v>46036</v>
       </c>
-      <c r="B15" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),315.85)</f>
+        <v>315.85</v>
       </c>
       <c r="C15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
+        <v>28.07555556</v>
       </c>
       <c r="D15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
+        <v>28.07555556</v>
       </c>
       <c r="E15" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
+        <v>28.07555556</v>
       </c>
       <c r="G15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
+        <v>28.07555556</v>
       </c>
       <c r="H15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
+        <v>28.07555556</v>
       </c>
       <c r="I15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
+        <v>28.07555556</v>
       </c>
       <c r="J15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
+        <v>28.07555556</v>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
+        <v>28.07555556</v>
       </c>
       <c r="L15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
+        <v>28.07555556</v>
       </c>
       <c r="M15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
+        <v>28.07555556</v>
       </c>
       <c r="N15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
+        <v>28.07555556</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1226,57 +1226,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46037.0)</f>
         <v>46037</v>
       </c>
-      <c r="B16" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),261.0)</f>
+        <v>261</v>
       </c>
       <c r="C16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
+        <v>23.2</v>
       </c>
       <c r="D16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
+        <v>23.2</v>
       </c>
       <c r="E16" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
+        <v>23.2</v>
       </c>
       <c r="G16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
+        <v>23.2</v>
       </c>
       <c r="H16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
+        <v>23.2</v>
       </c>
       <c r="I16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
+        <v>23.2</v>
       </c>
       <c r="J16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
+        <v>23.2</v>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
+        <v>23.2</v>
       </c>
       <c r="L16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
+        <v>23.2</v>
       </c>
       <c r="M16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
+        <v>23.2</v>
       </c>
       <c r="N16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
+        <v>23.2</v>
       </c>
       <c r="O16" s="1"/>
       <c r="P16" s="1">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1289,57 +1289,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46038.0)</f>
         <v>46038</v>
       </c>
-      <c r="B17" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
+        <v>328</v>
       </c>
       <c r="C17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
+        <v>29.15555556</v>
       </c>
       <c r="D17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
+        <v>29.15555556</v>
       </c>
       <c r="E17" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
+        <v>29.15555556</v>
       </c>
       <c r="G17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
+        <v>29.15555556</v>
       </c>
       <c r="H17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
+        <v>29.15555556</v>
       </c>
       <c r="I17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
+        <v>29.15555556</v>
       </c>
       <c r="J17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
+        <v>29.15555556</v>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
+        <v>29.15555556</v>
       </c>
       <c r="L17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
+        <v>29.15555556</v>
       </c>
       <c r="M17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
+        <v>29.15555556</v>
       </c>
       <c r="N17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
+        <v>29.15555556</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -20,10 +20,16 @@
     <numFmt numFmtId="164" formatCode="d/m"/>
     <numFmt numFmtId="165" formatCode="_([$R$ -416]* #,##0.00_);_([$R$ -416]* \(#,##0.00\);_([$R$ -416]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -47,15 +53,16 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -396,8 +403,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
         <v>23.01333333</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1">
+      <c r="O2" s="6"/>
+      <c r="P2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -459,8 +466,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.410000000000004)</f>
         <v>45.41</v>
       </c>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1">
+      <c r="O3" s="6"/>
+      <c r="P3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
         <v>8</v>
       </c>
@@ -522,8 +529,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.675)</f>
         <v>50.675</v>
       </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1">
+      <c r="O4" s="6"/>
+      <c r="P4" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
         <v>8</v>
       </c>
@@ -585,8 +592,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.8)</f>
         <v>49.8</v>
       </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1">
+      <c r="O5" s="6"/>
+      <c r="P5" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
         <v>8</v>
       </c>
@@ -648,8 +655,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
         <v>22.695</v>
       </c>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1">
+      <c r="O6" s="6"/>
+      <c r="P6" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
         <v>8</v>
       </c>
@@ -711,8 +718,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
         <v>21.77</v>
       </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1">
+      <c r="O7" s="6"/>
+      <c r="P7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
         <v>8</v>
       </c>
@@ -774,8 +781,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
         <v>35.455</v>
       </c>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1">
+      <c r="O8" s="6"/>
+      <c r="P8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
         <v>8</v>
       </c>
@@ -837,8 +844,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
         <v>26.565</v>
       </c>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1">
+      <c r="O9" s="6"/>
+      <c r="P9" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
         <v>8</v>
       </c>
@@ -900,8 +907,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
         <v>33.17</v>
       </c>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1">
+      <c r="O10" s="6"/>
+      <c r="P10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
         <v>8</v>
       </c>
@@ -963,8 +970,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
         <v>49.92</v>
       </c>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1">
+      <c r="O11" s="6"/>
+      <c r="P11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1026,8 +1033,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
         <v>45.38222222</v>
       </c>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1">
+      <c r="O12" s="6"/>
+      <c r="P12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1089,8 +1096,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
         <v>21.31555556</v>
       </c>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1">
+      <c r="O13" s="6"/>
+      <c r="P13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1152,8 +1159,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
         <v>16.79111111</v>
       </c>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1">
+      <c r="O14" s="6"/>
+      <c r="P14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1215,8 +1222,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
         <v>28.07555556</v>
       </c>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1">
+      <c r="O15" s="6"/>
+      <c r="P15" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1278,8 +1285,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
         <v>23.2</v>
       </c>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1">
+      <c r="O16" s="6"/>
+      <c r="P16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1341,8 +1348,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
         <v>29.15555556</v>
       </c>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1">
+      <c r="O17" s="6"/>
+      <c r="P17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1352,60 +1359,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46039.0)</f>
         <v>46039</v>
       </c>
-      <c r="B18" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),547.4)</f>
+        <v>547.4</v>
       </c>
       <c r="C18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
+        <v>48.65777778</v>
       </c>
       <c r="D18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
+        <v>48.65777778</v>
       </c>
       <c r="E18" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
+        <v>48.65777778</v>
       </c>
       <c r="G18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
+        <v>48.65777778</v>
       </c>
       <c r="H18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
+        <v>48.65777778</v>
       </c>
       <c r="I18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
+        <v>48.65777778</v>
       </c>
       <c r="J18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
+        <v>48.65777778</v>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
+        <v>48.65777778</v>
       </c>
       <c r="L18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
+        <v>48.65777778</v>
       </c>
       <c r="M18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
+        <v>48.65777778</v>
       </c>
       <c r="N18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
+        <v>48.65777778</v>
+      </c>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1467,8 +1474,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1">
+      <c r="O19" s="6"/>
+      <c r="P19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1530,8 +1537,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1">
+      <c r="O20" s="6"/>
+      <c r="P20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1593,8 +1600,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1">
+      <c r="O21" s="6"/>
+      <c r="P21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1656,8 +1663,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1">
+      <c r="O22" s="6"/>
+      <c r="P22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1719,8 +1726,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1">
+      <c r="O23" s="6"/>
+      <c r="P23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1782,8 +1789,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1">
+      <c r="O24" s="6"/>
+      <c r="P24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1845,8 +1852,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1">
+      <c r="O25" s="6"/>
+      <c r="P25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1908,8 +1915,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1">
+      <c r="O26" s="6"/>
+      <c r="P26" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1971,8 +1978,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1">
+      <c r="O27" s="6"/>
+      <c r="P27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -2034,8 +2041,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1">
+      <c r="O28" s="6"/>
+      <c r="P28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -2097,8 +2104,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1">
+      <c r="O29" s="6"/>
+      <c r="P29" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -2160,8 +2167,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1">
+      <c r="O30" s="6"/>
+      <c r="P30" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -2223,8 +2230,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1">
+      <c r="O31" s="6"/>
+      <c r="P31" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -2286,8 +2293,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1">
+      <c r="O32" s="6"/>
+      <c r="P32" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1422,57 +1422,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46040.0)</f>
         <v>46040</v>
       </c>
-      <c r="B19" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),622.1)</f>
+        <v>622.1</v>
       </c>
       <c r="C19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
+        <v>55.29777778</v>
       </c>
       <c r="D19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
+        <v>55.29777778</v>
       </c>
       <c r="E19" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
+        <v>55.29777778</v>
       </c>
       <c r="G19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
+        <v>55.29777778</v>
       </c>
       <c r="H19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
+        <v>55.29777778</v>
       </c>
       <c r="I19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
+        <v>55.29777778</v>
       </c>
       <c r="J19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
+        <v>55.29777778</v>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
+        <v>55.29777778</v>
       </c>
       <c r="L19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
+        <v>55.29777778</v>
       </c>
       <c r="M19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
+        <v>55.29777778</v>
       </c>
       <c r="N19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
+        <v>55.29777778</v>
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1485,57 +1485,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46041.0)</f>
         <v>46041</v>
       </c>
-      <c r="B20" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.8)</f>
+        <v>205.8</v>
       </c>
       <c r="C20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
+        <v>18.29333333</v>
       </c>
       <c r="D20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
+        <v>18.29333333</v>
       </c>
       <c r="E20" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
+        <v>18.29333333</v>
       </c>
       <c r="G20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
+        <v>18.29333333</v>
       </c>
       <c r="H20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
+        <v>18.29333333</v>
       </c>
       <c r="I20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
+        <v>18.29333333</v>
       </c>
       <c r="J20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
+        <v>18.29333333</v>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
+        <v>18.29333333</v>
       </c>
       <c r="L20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
+        <v>18.29333333</v>
       </c>
       <c r="M20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
+        <v>18.29333333</v>
       </c>
       <c r="N20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
+        <v>18.29333333</v>
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1548,57 +1548,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
         <v>46042</v>
       </c>
-      <c r="B21" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),654.4)</f>
+        <v>654.4</v>
       </c>
       <c r="C21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="D21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="E21" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="G21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="H21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="I21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="J21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="L21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="M21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="N21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="O21" s="6"/>
       <c r="P21" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1548,57 +1548,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
         <v>46042</v>
       </c>
-      <c r="B21" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),654.4)</f>
+        <v>654.4</v>
       </c>
       <c r="C21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="D21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="E21" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="G21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="H21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="I21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="J21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="L21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="M21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="N21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
+        <v>58.16888889</v>
       </c>
       <c r="O21" s="6"/>
       <c r="P21" s="6">
@@ -1611,57 +1611,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
         <v>46043</v>
       </c>
-      <c r="B22" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),171.95)</f>
+        <v>171.95</v>
       </c>
       <c r="C22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="D22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="E22" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="G22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="H22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="I22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="J22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="L22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="M22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="N22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1611,57 +1611,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
         <v>46043</v>
       </c>
-      <c r="B22" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),171.95)</f>
+        <v>171.95</v>
       </c>
       <c r="C22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="D22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="E22" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="G22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="H22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="I22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="J22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="L22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="M22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="N22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
+        <v>15.28444444</v>
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6">
@@ -1674,57 +1674,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46044.0)</f>
         <v>46044</v>
       </c>
-      <c r="B23" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),388.5)</f>
+        <v>388.5</v>
       </c>
       <c r="C23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
+        <v>34.53333333</v>
       </c>
       <c r="D23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
+        <v>34.53333333</v>
       </c>
       <c r="E23" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
+        <v>34.53333333</v>
       </c>
       <c r="G23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
+        <v>34.53333333</v>
       </c>
       <c r="H23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
+        <v>34.53333333</v>
       </c>
       <c r="I23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
+        <v>34.53333333</v>
       </c>
       <c r="J23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
+        <v>34.53333333</v>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
+        <v>34.53333333</v>
       </c>
       <c r="L23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
+        <v>34.53333333</v>
       </c>
       <c r="M23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
+        <v>34.53333333</v>
       </c>
       <c r="N23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
+        <v>34.53333333</v>
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1737,57 +1737,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46045.0)</f>
         <v>46045</v>
       </c>
-      <c r="B24" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),332.75)</f>
+        <v>332.75</v>
       </c>
       <c r="C24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
+        <v>29.57777778</v>
       </c>
       <c r="D24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
+        <v>29.57777778</v>
       </c>
       <c r="E24" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
+        <v>29.57777778</v>
       </c>
       <c r="G24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
+        <v>29.57777778</v>
       </c>
       <c r="H24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
+        <v>29.57777778</v>
       </c>
       <c r="I24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
+        <v>29.57777778</v>
       </c>
       <c r="J24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
+        <v>29.57777778</v>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
+        <v>29.57777778</v>
       </c>
       <c r="L24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
+        <v>29.57777778</v>
       </c>
       <c r="M24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
+        <v>29.57777778</v>
       </c>
       <c r="N24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
+        <v>29.57777778</v>
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1800,62 +1800,62 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46046.0)</f>
         <v>46046</v>
       </c>
-      <c r="B25" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),603.8)</f>
+        <v>603.8</v>
       </c>
       <c r="C25" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
+        <v>60.38</v>
       </c>
       <c r="D25" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
+        <v>60.38</v>
       </c>
       <c r="E25" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
+        <v>60.38</v>
       </c>
       <c r="G25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
+        <v>60.38</v>
+      </c>
+      <c r="H25" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
+        <v>60.38</v>
       </c>
       <c r="J25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
+        <v>60.38</v>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
+        <v>60.38</v>
       </c>
       <c r="L25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
+        <v>60.38</v>
       </c>
       <c r="M25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
+        <v>60.38</v>
       </c>
       <c r="N25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
+        <v>60.38</v>
       </c>
       <c r="O25" s="6"/>
       <c r="P25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -1887,9 +1887,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H26" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I26" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1917,8 +1917,8 @@
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="27">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1863,57 +1863,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46047.0)</f>
         <v>46047</v>
       </c>
-      <c r="B26" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),549.3)</f>
+        <v>549.3</v>
       </c>
       <c r="C26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="D26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="E26" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="G26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="H26" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="I26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="J26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="L26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="M26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="N26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1863,57 +1863,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46047.0)</f>
         <v>46047</v>
       </c>
-      <c r="B26" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),549.3)</f>
+        <v>549.3</v>
       </c>
       <c r="C26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="D26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="E26" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="G26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="H26" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="I26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="J26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="L26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="M26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="N26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
+        <v>54.93</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6">
@@ -1926,62 +1926,62 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46048.0)</f>
         <v>46048</v>
       </c>
-      <c r="B27" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.45)</f>
+        <v>177.45</v>
       </c>
       <c r="C27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
+        <v>17.745</v>
       </c>
       <c r="D27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
+        <v>17.745</v>
       </c>
       <c r="E27" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
+        <v>17.745</v>
       </c>
       <c r="G27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
+        <v>17.745</v>
+      </c>
+      <c r="H27" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
+        <v>17.745</v>
       </c>
       <c r="J27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
+        <v>17.745</v>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
+        <v>17.745</v>
       </c>
       <c r="L27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
+        <v>17.745</v>
       </c>
       <c r="M27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
+        <v>17.745</v>
       </c>
       <c r="N27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
+        <v>17.745</v>
       </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -2013,9 +2013,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H28" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I28" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2043,8 +2043,8 @@
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="29">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1989,57 +1989,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46049.0)</f>
         <v>46049</v>
       </c>
-      <c r="B28" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.3)</f>
+        <v>241.3</v>
       </c>
       <c r="C28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
+        <v>24.13</v>
       </c>
       <c r="D28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
+        <v>24.13</v>
       </c>
       <c r="E28" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
+        <v>24.13</v>
       </c>
       <c r="G28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
+        <v>24.13</v>
       </c>
       <c r="H28" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="I28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
+        <v>24.13</v>
       </c>
       <c r="J28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
+        <v>24.13</v>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
+        <v>24.13</v>
       </c>
       <c r="L28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
+        <v>24.13</v>
       </c>
       <c r="M28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
+        <v>24.13</v>
       </c>
       <c r="N28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
+        <v>24.13</v>
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -2052,57 +2052,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46050.0)</f>
         <v>46050</v>
       </c>
-      <c r="B29" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B29" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),389.85)</f>
+        <v>389.85</v>
       </c>
       <c r="C29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
+        <v>34.65333333</v>
       </c>
       <c r="D29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
+        <v>34.65333333</v>
       </c>
       <c r="E29" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
+        <v>34.65333333</v>
       </c>
       <c r="G29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
+        <v>34.65333333</v>
       </c>
       <c r="H29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
+        <v>34.65333333</v>
       </c>
       <c r="I29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
+        <v>34.65333333</v>
       </c>
       <c r="J29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
+        <v>34.65333333</v>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
+        <v>34.65333333</v>
       </c>
       <c r="L29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
+        <v>34.65333333</v>
       </c>
       <c r="M29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
+        <v>34.65333333</v>
       </c>
       <c r="N29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
+        <v>34.65333333</v>
       </c>
       <c r="O29" s="6"/>
       <c r="P29" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -2115,57 +2115,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46051.0)</f>
         <v>46051</v>
       </c>
-      <c r="B30" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B30" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),304.65)</f>
+        <v>304.65</v>
       </c>
       <c r="C30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
+        <v>27.08</v>
       </c>
       <c r="D30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
+        <v>27.08</v>
       </c>
       <c r="E30" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
+        <v>27.08</v>
       </c>
       <c r="G30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
+        <v>27.08</v>
       </c>
       <c r="H30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
+        <v>27.08</v>
       </c>
       <c r="I30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
+        <v>27.08</v>
       </c>
       <c r="J30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
+        <v>27.08</v>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
+        <v>27.08</v>
       </c>
       <c r="L30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
+        <v>27.08</v>
       </c>
       <c r="M30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
+        <v>27.08</v>
       </c>
       <c r="N30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
+        <v>27.08</v>
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -2178,57 +2178,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46052.0)</f>
         <v>46052</v>
       </c>
-      <c r="B31" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B31" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),197.2)</f>
+        <v>197.2</v>
       </c>
       <c r="C31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
+        <v>17.52888889</v>
       </c>
       <c r="D31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
+        <v>17.52888889</v>
       </c>
       <c r="E31" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
+        <v>17.52888889</v>
       </c>
       <c r="G31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
+        <v>17.52888889</v>
       </c>
       <c r="H31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
+        <v>17.52888889</v>
       </c>
       <c r="I31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
+        <v>17.52888889</v>
       </c>
       <c r="J31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
+        <v>17.52888889</v>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
+        <v>17.52888889</v>
       </c>
       <c r="L31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
+        <v>17.52888889</v>
       </c>
       <c r="M31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
+        <v>17.52888889</v>
       </c>
       <c r="N31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
+        <v>17.52888889</v>
       </c>
       <c r="O31" s="6"/>
       <c r="P31" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -2241,57 +2241,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46053.0)</f>
         <v>46053</v>
       </c>
-      <c r="B32" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B32" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.75)</f>
+        <v>409.75</v>
       </c>
       <c r="C32" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
+        <v>36.42222222</v>
       </c>
       <c r="D32" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
+        <v>36.42222222</v>
       </c>
       <c r="E32" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="F32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
+        <v>36.42222222</v>
       </c>
       <c r="G32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
+        <v>36.42222222</v>
       </c>
       <c r="H32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
+        <v>36.42222222</v>
       </c>
       <c r="I32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
+        <v>36.42222222</v>
       </c>
       <c r="J32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
+        <v>36.42222222</v>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
+        <v>36.42222222</v>
       </c>
       <c r="L32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
+        <v>36.42222222</v>
       </c>
       <c r="M32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
+        <v>36.42222222</v>
       </c>
       <c r="N32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
+        <v>36.42222222</v>
       </c>
       <c r="O32" s="6"/>
       <c r="P32" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -282,7 +282,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1POsjPVrSf7cI9l6RV9YTekpgPrIXrtJUSYTfH7IdCBw/edit?gid=1929580256#gid=1929580256"",""Janeiro!A1:P32"")"),"Data")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1POsjPVrSf7cI9l6RV9YTekpgPrIXrtJUSYTfH7IdCBw/edit?gid=1929580256#gid=1929580256"",""Fevereiro!A1:P32"")"),"Data")</f>
         <v>Data</v>
       </c>
       <c r="B1" s="1" t="str">
@@ -348,1955 +348,1946 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46023.0)</f>
-        <v>46023</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46054.0)</f>
+        <v>46054</v>
       </c>
       <c r="B2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.9)</f>
-        <v>258.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),576.85)</f>
+        <v>576.85</v>
       </c>
       <c r="C2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
-        <v>23.01333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
       </c>
       <c r="D2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
-        <v>23.01333333</v>
-      </c>
-      <c r="E2" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
+      </c>
+      <c r="E2" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
       </c>
       <c r="F2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
-        <v>23.01333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
       </c>
       <c r="G2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
-        <v>23.01333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
       </c>
       <c r="H2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
-        <v>23.01333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
       </c>
       <c r="I2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
-        <v>23.01333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
       </c>
       <c r="J2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
-        <v>23.01333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
-        <v>23.01333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
       </c>
       <c r="L2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
-        <v>23.01333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
       </c>
       <c r="M2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
-        <v>23.01333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
       </c>
       <c r="N2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.013333333333332)</f>
-        <v>23.01333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
+        <v>46.148</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46024.0)</f>
-        <v>46024</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46055.0)</f>
+        <v>46055</v>
       </c>
       <c r="B3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),454.1)</f>
-        <v>454.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),190.3)</f>
+        <v>190.3</v>
       </c>
       <c r="C3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.410000000000004)</f>
-        <v>45.41</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
       </c>
       <c r="D3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.410000000000004)</f>
-        <v>45.41</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
+      </c>
+      <c r="E3" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
       </c>
       <c r="F3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.410000000000004)</f>
-        <v>45.41</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
       </c>
       <c r="G3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.410000000000004)</f>
-        <v>45.41</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
       </c>
       <c r="H3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.410000000000004)</f>
-        <v>45.41</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
       </c>
       <c r="I3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.410000000000004)</f>
-        <v>45.41</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
       </c>
       <c r="J3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.410000000000004)</f>
-        <v>45.41</v>
-      </c>
-      <c r="K3" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
+      </c>
+      <c r="K3" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
       </c>
       <c r="L3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.410000000000004)</f>
-        <v>45.41</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
       </c>
       <c r="M3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.410000000000004)</f>
-        <v>45.41</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
       </c>
       <c r="N3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.410000000000004)</f>
-        <v>45.41</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
+        <v>15.224</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46025.0)</f>
-        <v>46025</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46056.0)</f>
+        <v>46056</v>
       </c>
       <c r="B4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),506.75)</f>
-        <v>506.75</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),233.3)</f>
+        <v>233.3</v>
       </c>
       <c r="C4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.675)</f>
-        <v>50.675</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="D4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.675)</f>
-        <v>50.675</v>
-      </c>
-      <c r="E4" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.675)</f>
-        <v>50.675</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.675)</f>
-        <v>50.675</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.675)</f>
-        <v>50.675</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.675)</f>
-        <v>50.675</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.675)</f>
-        <v>50.675</v>
-      </c>
-      <c r="K4" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.675)</f>
-        <v>50.675</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.675)</f>
-        <v>50.675</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.675)</f>
-        <v>50.675</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46026.0)</f>
-        <v>46026</v>
-      </c>
-      <c r="B5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),498.0)</f>
-        <v>498</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46057.0)</f>
+        <v>46057</v>
+      </c>
+      <c r="B5" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.8)</f>
-        <v>49.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.8)</f>
-        <v>49.8</v>
-      </c>
-      <c r="E5" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.8)</f>
-        <v>49.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.8)</f>
-        <v>49.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.8)</f>
-        <v>49.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.8)</f>
-        <v>49.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.8)</f>
-        <v>49.8</v>
-      </c>
-      <c r="K5" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.8)</f>
-        <v>49.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.8)</f>
-        <v>49.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.8)</f>
-        <v>49.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46027.0)</f>
-        <v>46027</v>
-      </c>
-      <c r="B6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),226.95)</f>
-        <v>226.95</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46058.0)</f>
+        <v>46058</v>
+      </c>
+      <c r="B6" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
-        <v>22.695</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
-        <v>22.695</v>
-      </c>
-      <c r="E6" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
-        <v>22.695</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
-        <v>22.695</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
-        <v>22.695</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
-        <v>22.695</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
-        <v>22.695</v>
-      </c>
-      <c r="K6" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
-        <v>22.695</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
-        <v>22.695</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.695)</f>
-        <v>22.695</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46028.0)</f>
-        <v>46028</v>
-      </c>
-      <c r="B7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.7)</f>
-        <v>217.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46059.0)</f>
+        <v>46059</v>
+      </c>
+      <c r="B7" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
-        <v>21.77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
-        <v>21.77</v>
-      </c>
-      <c r="E7" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
-        <v>21.77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
-        <v>21.77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
-        <v>21.77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
-        <v>21.77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
-        <v>21.77</v>
-      </c>
-      <c r="K7" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
-        <v>21.77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
-        <v>21.77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.77)</f>
-        <v>21.77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46029.0)</f>
-        <v>46029</v>
-      </c>
-      <c r="B8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),354.55)</f>
-        <v>354.55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46060.0)</f>
+        <v>46060</v>
+      </c>
+      <c r="B8" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
-        <v>35.455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
-        <v>35.455</v>
-      </c>
-      <c r="E8" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
-        <v>35.455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
-        <v>35.455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
-        <v>35.455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
-        <v>35.455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
-        <v>35.455</v>
-      </c>
-      <c r="K8" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
-        <v>35.455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
-        <v>35.455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.455)</f>
-        <v>35.455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46030.0)</f>
-        <v>46030</v>
-      </c>
-      <c r="B9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),265.65)</f>
-        <v>265.65</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46061.0)</f>
+        <v>46061</v>
+      </c>
+      <c r="B9" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
-        <v>26.565</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
-        <v>26.565</v>
-      </c>
-      <c r="E9" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
-        <v>26.565</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
-        <v>26.565</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
-        <v>26.565</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
-        <v>26.565</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
-        <v>26.565</v>
-      </c>
-      <c r="K9" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
-        <v>26.565</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
-        <v>26.565</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.564999999999998)</f>
-        <v>26.565</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O9" s="6"/>
       <c r="P9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46031.0)</f>
-        <v>46031</v>
-      </c>
-      <c r="B10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331.7)</f>
-        <v>331.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46062.0)</f>
+        <v>46062</v>
+      </c>
+      <c r="B10" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
-        <v>33.17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
-        <v>33.17</v>
-      </c>
-      <c r="E10" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
-        <v>33.17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
-        <v>33.17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
-        <v>33.17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
-        <v>33.17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
-        <v>33.17</v>
-      </c>
-      <c r="K10" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
-        <v>33.17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
-        <v>33.17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.17)</f>
-        <v>33.17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46032.0)</f>
-        <v>46032</v>
-      </c>
-      <c r="B11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),561.6)</f>
-        <v>561.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46063.0)</f>
+        <v>46063</v>
+      </c>
+      <c r="B11" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
-        <v>49.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
-        <v>49.92</v>
-      </c>
-      <c r="E11" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
-        <v>49.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
-        <v>49.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
-        <v>49.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
-        <v>49.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
-        <v>49.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
-        <v>49.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
-        <v>49.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
-        <v>49.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.92)</f>
-        <v>49.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46033.0)</f>
-        <v>46033</v>
-      </c>
-      <c r="B12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),510.55)</f>
-        <v>510.55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46064.0)</f>
+        <v>46064</v>
+      </c>
+      <c r="B12" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
-        <v>45.38222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
-        <v>45.38222222</v>
-      </c>
-      <c r="E12" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
-        <v>45.38222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
-        <v>45.38222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
-        <v>45.38222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
-        <v>45.38222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
-        <v>45.38222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
-        <v>45.38222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
-        <v>45.38222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
-        <v>45.38222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.382222222222225)</f>
-        <v>45.38222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46034.0)</f>
-        <v>46034</v>
-      </c>
-      <c r="B13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),239.8)</f>
-        <v>239.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46065.0)</f>
+        <v>46065</v>
+      </c>
+      <c r="B13" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
-        <v>21.31555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
-        <v>21.31555556</v>
-      </c>
-      <c r="E13" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
-        <v>21.31555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
-        <v>21.31555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
-        <v>21.31555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
-        <v>21.31555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
-        <v>21.31555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
-        <v>21.31555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
-        <v>21.31555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
-        <v>21.31555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.315555555555555)</f>
-        <v>21.31555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46035.0)</f>
-        <v>46035</v>
-      </c>
-      <c r="B14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),188.9)</f>
-        <v>188.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46066.0)</f>
+        <v>46066</v>
+      </c>
+      <c r="B14" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
-        <v>16.79111111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
-        <v>16.79111111</v>
-      </c>
-      <c r="E14" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
-        <v>16.79111111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
-        <v>16.79111111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
-        <v>16.79111111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
-        <v>16.79111111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
-        <v>16.79111111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
-        <v>16.79111111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
-        <v>16.79111111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
-        <v>16.79111111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.791111111111114)</f>
-        <v>16.79111111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46036.0)</f>
-        <v>46036</v>
-      </c>
-      <c r="B15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),315.85)</f>
-        <v>315.85</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46067.0)</f>
+        <v>46067</v>
+      </c>
+      <c r="B15" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
-        <v>28.07555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
-        <v>28.07555556</v>
-      </c>
-      <c r="E15" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
-        <v>28.07555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
-        <v>28.07555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
-        <v>28.07555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
-        <v>28.07555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
-        <v>28.07555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
-        <v>28.07555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
-        <v>28.07555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
-        <v>28.07555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.07555555555556)</f>
-        <v>28.07555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O15" s="6"/>
       <c r="P15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46037.0)</f>
-        <v>46037</v>
-      </c>
-      <c r="B16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),261.0)</f>
-        <v>261</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46068.0)</f>
+        <v>46068</v>
+      </c>
+      <c r="B16" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
-        <v>23.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
-        <v>23.2</v>
-      </c>
-      <c r="E16" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
-        <v>23.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
-        <v>23.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
-        <v>23.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
-        <v>23.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
-        <v>23.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
-        <v>23.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
-        <v>23.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
-        <v>23.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.2)</f>
-        <v>23.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46038.0)</f>
-        <v>46038</v>
-      </c>
-      <c r="B17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),328.0)</f>
-        <v>328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46069.0)</f>
+        <v>46069</v>
+      </c>
+      <c r="B17" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
-        <v>29.15555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
-        <v>29.15555556</v>
-      </c>
-      <c r="E17" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
-        <v>29.15555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
-        <v>29.15555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
-        <v>29.15555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
-        <v>29.15555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
-        <v>29.15555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
-        <v>29.15555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
-        <v>29.15555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
-        <v>29.15555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.155555555555555)</f>
-        <v>29.15555556</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O17" s="6"/>
       <c r="P17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46039.0)</f>
-        <v>46039</v>
-      </c>
-      <c r="B18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),547.4)</f>
-        <v>547.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46070.0)</f>
+        <v>46070</v>
+      </c>
+      <c r="B18" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
-        <v>48.65777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
-        <v>48.65777778</v>
-      </c>
-      <c r="E18" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
-        <v>48.65777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
-        <v>48.65777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
-        <v>48.65777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
-        <v>48.65777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
-        <v>48.65777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
-        <v>48.65777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
-        <v>48.65777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
-        <v>48.65777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.65777777777778)</f>
-        <v>48.65777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46040.0)</f>
-        <v>46040</v>
-      </c>
-      <c r="B19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),622.1)</f>
-        <v>622.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46071.0)</f>
+        <v>46071</v>
+      </c>
+      <c r="B19" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
-        <v>55.29777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
-        <v>55.29777778</v>
-      </c>
-      <c r="E19" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
-        <v>55.29777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
-        <v>55.29777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
-        <v>55.29777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
-        <v>55.29777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
-        <v>55.29777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
-        <v>55.29777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
-        <v>55.29777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
-        <v>55.29777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.297777777777775)</f>
-        <v>55.29777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46041.0)</f>
-        <v>46041</v>
-      </c>
-      <c r="B20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),205.8)</f>
-        <v>205.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46072.0)</f>
+        <v>46072</v>
+      </c>
+      <c r="B20" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
-        <v>18.29333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
-        <v>18.29333333</v>
-      </c>
-      <c r="E20" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
-        <v>18.29333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
-        <v>18.29333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
-        <v>18.29333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
-        <v>18.29333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
-        <v>18.29333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
-        <v>18.29333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
-        <v>18.29333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
-        <v>18.29333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.293333333333333)</f>
-        <v>18.29333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
-        <v>46042</v>
-      </c>
-      <c r="B21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),654.4)</f>
-        <v>654.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46073.0)</f>
+        <v>46073</v>
+      </c>
+      <c r="B21" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
-        <v>58.16888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
-        <v>58.16888889</v>
-      </c>
-      <c r="E21" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
-        <v>58.16888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
-        <v>58.16888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
-        <v>58.16888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
-        <v>58.16888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
-        <v>58.16888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
-        <v>58.16888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
-        <v>58.16888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
-        <v>58.16888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.16888888888889)</f>
-        <v>58.16888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O21" s="6"/>
       <c r="P21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
-        <v>46043</v>
-      </c>
-      <c r="B22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),171.95)</f>
-        <v>171.95</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46074.0)</f>
+        <v>46074</v>
+      </c>
+      <c r="B22" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
-        <v>15.28444444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
-        <v>15.28444444</v>
-      </c>
-      <c r="E22" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
-        <v>15.28444444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
-        <v>15.28444444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
-        <v>15.28444444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
-        <v>15.28444444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
-        <v>15.28444444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
-        <v>15.28444444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
-        <v>15.28444444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
-        <v>15.28444444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.284444444444443)</f>
-        <v>15.28444444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46044.0)</f>
-        <v>46044</v>
-      </c>
-      <c r="B23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),388.5)</f>
-        <v>388.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46075.0)</f>
+        <v>46075</v>
+      </c>
+      <c r="B23" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
-        <v>34.53333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
-        <v>34.53333333</v>
-      </c>
-      <c r="E23" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
-        <v>34.53333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
-        <v>34.53333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
-        <v>34.53333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
-        <v>34.53333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
-        <v>34.53333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
-        <v>34.53333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
-        <v>34.53333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
-        <v>34.53333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.53333333333333)</f>
-        <v>34.53333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46045.0)</f>
-        <v>46045</v>
-      </c>
-      <c r="B24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),332.75)</f>
-        <v>332.75</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46076.0)</f>
+        <v>46076</v>
+      </c>
+      <c r="B24" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
-        <v>29.57777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
-        <v>29.57777778</v>
-      </c>
-      <c r="E24" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
-        <v>29.57777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
-        <v>29.57777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
-        <v>29.57777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
-        <v>29.57777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
-        <v>29.57777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
-        <v>29.57777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
-        <v>29.57777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
-        <v>29.57777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.577777777777776)</f>
-        <v>29.57777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46046.0)</f>
-        <v>46046</v>
-      </c>
-      <c r="B25" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),603.8)</f>
-        <v>603.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46077.0)</f>
+        <v>46077</v>
+      </c>
+      <c r="B25" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C25" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
-        <v>60.38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D25" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
-        <v>60.38</v>
-      </c>
-      <c r="E25" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
-        <v>60.38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
-        <v>60.38</v>
-      </c>
-      <c r="H25" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
-        <v>60.38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
-        <v>60.38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
-        <v>60.38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
-        <v>60.38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
-        <v>60.38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.379999999999995)</f>
-        <v>60.38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O25" s="6"/>
       <c r="P25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46047.0)</f>
-        <v>46047</v>
-      </c>
-      <c r="B26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),549.3)</f>
-        <v>549.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46078.0)</f>
+        <v>46078</v>
+      </c>
+      <c r="B26" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
-        <v>54.93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
-        <v>54.93</v>
-      </c>
-      <c r="E26" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
-        <v>54.93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
-        <v>54.93</v>
-      </c>
-      <c r="H26" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
-        <v>54.93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
-        <v>54.93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
-        <v>54.93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
-        <v>54.93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
-        <v>54.93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.92999999999999)</f>
-        <v>54.93</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46048.0)</f>
-        <v>46048</v>
-      </c>
-      <c r="B27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.45)</f>
-        <v>177.45</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46079.0)</f>
+        <v>46079</v>
+      </c>
+      <c r="B27" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
-        <v>17.745</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
-        <v>17.745</v>
-      </c>
-      <c r="E27" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
-        <v>17.745</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
-        <v>17.745</v>
-      </c>
-      <c r="H27" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
-        <v>17.745</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
-        <v>17.745</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
-        <v>17.745</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
-        <v>17.745</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
-        <v>17.745</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.744999999999997)</f>
-        <v>17.745</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46049.0)</f>
-        <v>46049</v>
-      </c>
-      <c r="B28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.3)</f>
-        <v>241.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46080.0)</f>
+        <v>46080</v>
+      </c>
+      <c r="B28" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
-        <v>24.13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
-        <v>24.13</v>
-      </c>
-      <c r="E28" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
-        <v>24.13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
-        <v>24.13</v>
-      </c>
-      <c r="H28" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
-        <v>24.13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
-        <v>24.13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
-        <v>24.13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
-        <v>24.13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
-        <v>24.13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.130000000000003)</f>
-        <v>24.13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46050.0)</f>
-        <v>46050</v>
-      </c>
-      <c r="B29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),389.85)</f>
-        <v>389.85</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46081.0)</f>
+        <v>46081</v>
+      </c>
+      <c r="B29" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
-        <v>34.65333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
-        <v>34.65333333</v>
-      </c>
-      <c r="E29" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
-        <v>34.65333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
-        <v>34.65333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
-        <v>34.65333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
-        <v>34.65333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
-        <v>34.65333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
-        <v>34.65333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
-        <v>34.65333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
-        <v>34.65333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.653333333333336)</f>
-        <v>34.65333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O29" s="6"/>
       <c r="P29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46051.0)</f>
-        <v>46051</v>
-      </c>
-      <c r="B30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),304.65)</f>
-        <v>304.65</v>
+      <c r="A30" s="6"/>
+      <c r="B30" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
-        <v>27.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
-        <v>27.08</v>
-      </c>
-      <c r="E30" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
-        <v>27.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
-        <v>27.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
-        <v>27.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
-        <v>27.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
-        <v>27.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
-        <v>27.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
-        <v>27.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
-        <v>27.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.079999999999995)</f>
-        <v>27.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46052.0)</f>
-        <v>46052</v>
-      </c>
-      <c r="B31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),197.2)</f>
-        <v>197.2</v>
+      <c r="A31" s="6"/>
+      <c r="B31" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
-        <v>17.52888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
-        <v>17.52888889</v>
-      </c>
-      <c r="E31" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
-        <v>17.52888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
-        <v>17.52888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
-        <v>17.52888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
-        <v>17.52888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
-        <v>17.52888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
-        <v>17.52888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
-        <v>17.52888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
-        <v>17.52888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.52888888888889)</f>
-        <v>17.52888889</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O31" s="6"/>
       <c r="P31" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46053.0)</f>
-        <v>46053</v>
-      </c>
-      <c r="B32" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),409.75)</f>
-        <v>409.75</v>
+      <c r="A32" s="6"/>
+      <c r="B32" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
+        <v/>
       </c>
       <c r="C32" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
-        <v>36.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D32" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
-        <v>36.42222222</v>
-      </c>
-      <c r="E32" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
-        <v>36.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
-        <v>36.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
-        <v>36.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
-        <v>36.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
-        <v>36.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
-        <v>36.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
-        <v>36.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
-        <v>36.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="N32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.422222222222224)</f>
-        <v>36.42222222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="O32" s="6"/>
       <c r="P32" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -486,48 +486,48 @@
         <v>18.664</v>
       </c>
       <c r="D4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="E4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="F4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="G4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="H4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="I4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="J4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="L4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="M4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="N4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
+        <v>18.664</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6">
@@ -540,57 +540,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46057.0)</f>
         <v>46057</v>
       </c>
-      <c r="B5" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.55)</f>
+        <v>231.55</v>
       </c>
       <c r="C5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="D5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="E5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="F5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="G5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="H5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="I5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="J5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
+        <v>18.524</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6">

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -337,14 +337,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Naiane")</f>
         <v>Naiane</v>
       </c>
-      <c r="O1" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Coluna 15")</f>
-        <v>Coluna 15</v>
-      </c>
-      <c r="P1" s="1" t="str">
+      <c r="O1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Colaboradores")</f>
         <v>Colaboradores</v>
       </c>
+      <c r="P1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="3">
@@ -356,57 +353,56 @@
         <v>576.85</v>
       </c>
       <c r="C2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
       </c>
       <c r="D2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
       </c>
       <c r="E2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
       </c>
       <c r="F2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
       </c>
       <c r="G2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
-      </c>
-      <c r="H2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
       </c>
       <c r="J2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
       </c>
       <c r="L2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
       </c>
       <c r="M2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
       </c>
       <c r="N2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.148)</f>
-        <v>46.148</v>
-      </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
+      </c>
+      <c r="O2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -419,57 +415,56 @@
         <v>190.3</v>
       </c>
       <c r="C3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
       </c>
       <c r="D3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
       </c>
       <c r="E3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
       </c>
       <c r="F3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
       </c>
       <c r="G3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
-      </c>
-      <c r="H3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
       </c>
       <c r="J3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
       </c>
       <c r="L3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
       </c>
       <c r="M3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
       </c>
       <c r="N3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.224)</f>
-        <v>15.224</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
+      </c>
+      <c r="O3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -482,57 +477,56 @@
         <v>233.3</v>
       </c>
       <c r="C4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
       </c>
       <c r="D4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
       </c>
       <c r="E4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
       </c>
       <c r="F4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
       </c>
       <c r="G4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
-      </c>
-      <c r="H4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
+      </c>
+      <c r="H4" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
       </c>
       <c r="J4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
       </c>
       <c r="L4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
       </c>
       <c r="M4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
       </c>
       <c r="N4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.664)</f>
-        <v>18.664</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
+      </c>
+      <c r="O4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -545,57 +539,56 @@
         <v>231.55</v>
       </c>
       <c r="C5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
       </c>
       <c r="D5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
       </c>
       <c r="E5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
       </c>
       <c r="F5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
       </c>
       <c r="G5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
-      </c>
-      <c r="H5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
+      </c>
+      <c r="H5" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
       </c>
       <c r="J5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.524)</f>
-        <v>18.524</v>
-      </c>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
+      </c>
+      <c r="O5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -603,62 +596,61 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46058.0)</f>
         <v>46058</v>
       </c>
-      <c r="B6" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),282.0)</f>
+        <v>282</v>
       </c>
       <c r="C6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
       </c>
       <c r="D6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
       </c>
       <c r="E6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
       </c>
       <c r="F6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
       </c>
       <c r="G6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
+      </c>
+      <c r="H6" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
       </c>
       <c r="J6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
+      </c>
+      <c r="O6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -690,9 +682,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H7" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I7" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -718,10 +710,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -753,9 +744,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H8" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I8" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -781,10 +772,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -816,9 +806,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H9" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I9" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -844,10 +834,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -879,9 +868,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H10" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I10" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -907,10 +896,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -942,9 +930,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H11" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I11" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -970,10 +958,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1005,9 +992,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H12" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I12" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1033,10 +1020,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1068,9 +1054,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H13" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I13" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1096,10 +1082,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1131,9 +1116,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H14" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I14" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1159,10 +1144,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -1194,9 +1178,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H15" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I15" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1222,10 +1206,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1257,9 +1240,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H16" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I16" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1285,10 +1268,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -1320,9 +1302,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H17" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I17" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1348,10 +1330,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -1383,9 +1364,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H18" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I18" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1411,10 +1392,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -1446,9 +1426,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H19" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I19" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1474,10 +1454,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -1509,9 +1488,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H20" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I20" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1537,10 +1516,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -1572,9 +1550,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H21" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I21" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1600,10 +1578,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -1635,9 +1612,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H22" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I22" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1663,10 +1640,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1698,9 +1674,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H23" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I23" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1726,10 +1702,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1761,9 +1736,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H24" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I24" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1789,10 +1764,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1824,9 +1798,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H25" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I25" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1852,10 +1826,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -1887,9 +1860,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H26" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I26" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1915,10 +1888,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -1950,9 +1922,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H27" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I27" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1978,10 +1950,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -2013,9 +1984,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H28" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I28" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2041,10 +2012,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -2076,9 +2046,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H29" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I29" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2104,10 +2074,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -2136,9 +2105,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H30" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I30" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2164,10 +2133,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O30" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -2196,9 +2164,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H31" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I31" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2224,10 +2192,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O31" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -2256,9 +2223,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="H32" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="I32" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2284,10 +2251,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="O32" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -658,57 +658,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46059.0)</f>
         <v>46059</v>
       </c>
-      <c r="B7" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258.25)</f>
+        <v>258.25</v>
       </c>
       <c r="C7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="D7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="E7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="F7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="G7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="H7" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="I7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="J7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="O7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -720,57 +720,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46060.0)</f>
         <v>46060</v>
       </c>
-      <c r="B8" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),476.95)</f>
+        <v>476.95</v>
       </c>
       <c r="C8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="D8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="E8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="F8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="G8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="H8" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="I8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="J8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="L8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="M8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="N8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="O8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
@@ -782,57 +782,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46061.0)</f>
         <v>46061</v>
       </c>
-      <c r="B9" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),670.0)</f>
+        <v>670</v>
       </c>
       <c r="C9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="D9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="E9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="F9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="G9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="H9" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="I9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="J9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="L9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="M9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="N9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="O9" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -844,57 +844,57 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46062.0)</f>
         <v>46062</v>
       </c>
-      <c r="B10" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.45)</f>
+        <v>355.45</v>
       </c>
       <c r="C10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="D10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="E10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="F10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="G10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="H10" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="I10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="J10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="L10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="M10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="N10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="O10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -310,37 +310,34 @@
         <v>Jaqueline</v>
       </c>
       <c r="H1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Gabriela")</f>
-        <v>Gabriela</v>
-      </c>
-      <c r="I1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fábio")</f>
         <v>Fábio</v>
       </c>
-      <c r="J1" s="1" t="str">
+      <c r="I1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fátima")</f>
         <v>Fátima</v>
       </c>
-      <c r="K1" s="1" t="str">
+      <c r="J1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jessyca")</f>
         <v>Jessyca</v>
       </c>
-      <c r="L1" s="2" t="str">
+      <c r="K1" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Jesiana")</f>
         <v>Jesiana</v>
       </c>
-      <c r="M1" s="2" t="str">
+      <c r="L1" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alexandro")</f>
         <v>Alexandro</v>
       </c>
-      <c r="N1" s="2" t="str">
+      <c r="M1" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Naiane")</f>
         <v>Naiane</v>
       </c>
-      <c r="O1" s="1" t="str">
+      <c r="N1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Colaboradores")</f>
         <v>Colaboradores</v>
       </c>
+      <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
     <row r="2">
@@ -372,9 +369,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
         <v>51.27555556</v>
       </c>
-      <c r="H2" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H2" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
+        <v>51.27555556</v>
       </c>
       <c r="I2" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
@@ -396,11 +393,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
         <v>51.27555556</v>
       </c>
-      <c r="N2" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.275555555555556)</f>
-        <v>51.27555556</v>
-      </c>
-      <c r="O2" s="6">
+      <c r="N2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -434,9 +427,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
         <v>16.91555556</v>
       </c>
-      <c r="H3" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H3" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
+        <v>16.91555556</v>
       </c>
       <c r="I3" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
@@ -458,11 +451,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
         <v>16.91555556</v>
       </c>
-      <c r="N3" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.915555555555557)</f>
-        <v>16.91555556</v>
-      </c>
-      <c r="O3" s="6">
+      <c r="N3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -496,9 +485,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
         <v>20.73777778</v>
       </c>
-      <c r="H4" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H4" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
+        <v>20.73777778</v>
       </c>
       <c r="I4" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
@@ -520,11 +509,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
         <v>20.73777778</v>
       </c>
-      <c r="N4" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.73777777777778)</f>
-        <v>20.73777778</v>
-      </c>
-      <c r="O4" s="6">
+      <c r="N4" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -558,9 +543,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
         <v>20.58222222</v>
       </c>
-      <c r="H5" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H5" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
+        <v>20.58222222</v>
       </c>
       <c r="I5" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
@@ -582,11 +567,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
         <v>20.58222222</v>
       </c>
-      <c r="N5" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.58222222222222)</f>
-        <v>20.58222222</v>
-      </c>
-      <c r="O5" s="6">
+      <c r="N5" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -620,9 +601,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
         <v>25.06666667</v>
       </c>
-      <c r="H6" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H6" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
+        <v>25.06666667</v>
       </c>
       <c r="I6" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
@@ -644,11 +625,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
         <v>25.06666667</v>
       </c>
-      <c r="N6" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.066666666666666)</f>
-        <v>25.06666667</v>
-      </c>
-      <c r="O6" s="6">
+      <c r="N6" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -682,9 +659,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
         <v>22.95555556</v>
       </c>
-      <c r="H7" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H7" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
+        <v>22.95555556</v>
       </c>
       <c r="I7" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
@@ -706,11 +683,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
         <v>22.95555556</v>
       </c>
-      <c r="N7" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.955555555555556)</f>
-        <v>22.95555556</v>
-      </c>
-      <c r="O7" s="6">
+      <c r="N7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -744,9 +717,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
         <v>42.39555556</v>
       </c>
-      <c r="H8" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H8" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
+        <v>42.39555556</v>
       </c>
       <c r="I8" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
@@ -768,11 +741,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
         <v>42.39555556</v>
       </c>
-      <c r="N8" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.39555555555555)</f>
-        <v>42.39555556</v>
-      </c>
-      <c r="O8" s="6">
+      <c r="N8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -806,9 +775,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
         <v>59.55555556</v>
       </c>
-      <c r="H9" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H9" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
+        <v>59.55555556</v>
       </c>
       <c r="I9" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
@@ -830,11 +799,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
         <v>59.55555556</v>
       </c>
-      <c r="N9" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.55555555555556)</f>
-        <v>59.55555556</v>
-      </c>
-      <c r="O9" s="6">
+      <c r="N9" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -868,9 +833,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
         <v>31.59555556</v>
       </c>
-      <c r="H10" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H10" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
+        <v>31.59555556</v>
       </c>
       <c r="I10" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
@@ -892,11 +857,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
         <v>31.59555556</v>
       </c>
-      <c r="N10" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.595555555555553)</f>
-        <v>31.59555556</v>
-      </c>
-      <c r="O10" s="6">
+      <c r="N10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -906,59 +867,55 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46063.0)</f>
         <v>46063</v>
       </c>
-      <c r="B11" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),296.1)</f>
+        <v>296.1</v>
       </c>
       <c r="C11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.320000000000004)</f>
+        <v>26.32</v>
       </c>
       <c r="D11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.320000000000004)</f>
+        <v>26.32</v>
       </c>
       <c r="E11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.320000000000004)</f>
+        <v>26.32</v>
       </c>
       <c r="F11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.320000000000004)</f>
+        <v>26.32</v>
       </c>
       <c r="G11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.320000000000004)</f>
+        <v>26.32</v>
+      </c>
+      <c r="H11" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.320000000000004)</f>
+        <v>26.32</v>
       </c>
       <c r="I11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.320000000000004)</f>
+        <v>26.32</v>
       </c>
       <c r="J11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.320000000000004)</f>
+        <v>26.32</v>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.320000000000004)</f>
+        <v>26.32</v>
       </c>
       <c r="L11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.320000000000004)</f>
+        <v>26.32</v>
       </c>
       <c r="M11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.320000000000004)</f>
+        <v>26.32</v>
+      </c>
+      <c r="N11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -992,9 +949,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H12" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I12" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1016,11 +973,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O12" s="6">
+      <c r="N12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1054,9 +1007,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H13" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I13" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1078,11 +1031,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="6">
+      <c r="N13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1116,9 +1065,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H14" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I14" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1140,11 +1089,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="6">
+      <c r="N14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1178,9 +1123,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H15" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I15" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1202,11 +1147,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O15" s="6">
+      <c r="N15" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1240,9 +1181,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H16" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I16" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1264,11 +1205,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O16" s="6">
+      <c r="N16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1302,9 +1239,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H17" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I17" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1326,11 +1263,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O17" s="6">
+      <c r="N17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1364,9 +1297,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H18" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I18" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1388,11 +1321,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O18" s="6">
+      <c r="N18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1426,9 +1355,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H19" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I19" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1450,11 +1379,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O19" s="6">
+      <c r="N19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1488,9 +1413,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H20" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I20" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1512,11 +1437,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O20" s="6">
+      <c r="N20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1550,9 +1471,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H21" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I21" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1574,11 +1495,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="6">
+      <c r="N21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1612,9 +1529,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H22" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I22" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1636,11 +1553,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O22" s="6">
+      <c r="N22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1674,9 +1587,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H23" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I23" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1698,11 +1611,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O23" s="6">
+      <c r="N23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1736,9 +1645,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H24" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I24" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1760,11 +1669,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O24" s="6">
+      <c r="N24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1798,9 +1703,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H25" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I25" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1822,11 +1727,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="6">
+      <c r="N25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1860,9 +1761,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H26" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I26" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1884,11 +1785,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O26" s="6">
+      <c r="N26" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1922,9 +1819,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H27" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I27" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1946,11 +1843,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O27" s="6">
+      <c r="N27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -1984,9 +1877,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H28" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I28" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2008,11 +1901,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="6">
+      <c r="N28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -2046,9 +1935,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H29" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H29" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I29" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2070,11 +1959,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O29" s="6">
+      <c r="N29" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -2105,9 +1990,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H30" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I30" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2129,11 +2014,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O30" s="6">
+      <c r="N30" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -2164,9 +2045,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H31" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H31" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I31" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2188,11 +2069,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O31" s="6">
+      <c r="N31" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>
@@ -2223,9 +2100,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H32" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
-        <v>x</v>
+      <c r="H32" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I32" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2247,11 +2124,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O32" s="6">
+      <c r="N32" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
         <v>9</v>
       </c>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -925,53 +925,53 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46064.0)</f>
         <v>46064</v>
       </c>
-      <c r="B12" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),425.3)</f>
+        <v>425.3</v>
       </c>
       <c r="C12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.80444444444445)</f>
+        <v>37.80444444</v>
       </c>
       <c r="D12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.80444444444445)</f>
+        <v>37.80444444</v>
       </c>
       <c r="E12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.80444444444445)</f>
+        <v>37.80444444</v>
       </c>
       <c r="F12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.80444444444445)</f>
+        <v>37.80444444</v>
       </c>
       <c r="G12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.80444444444445)</f>
+        <v>37.80444444</v>
       </c>
       <c r="H12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.80444444444445)</f>
+        <v>37.80444444</v>
       </c>
       <c r="I12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.80444444444445)</f>
+        <v>37.80444444</v>
       </c>
       <c r="J12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.80444444444445)</f>
+        <v>37.80444444</v>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.80444444444445)</f>
+        <v>37.80444444</v>
       </c>
       <c r="L12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.80444444444445)</f>
+        <v>37.80444444</v>
       </c>
       <c r="M12" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.80444444444445)</f>
+        <v>37.80444444</v>
       </c>
       <c r="N12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -983,53 +983,53 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46065.0)</f>
         <v>46065</v>
       </c>
-      <c r="B13" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
+        <v>117</v>
       </c>
       <c r="C13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4)</f>
+        <v>10.4</v>
       </c>
       <c r="D13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4)</f>
+        <v>10.4</v>
       </c>
       <c r="E13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4)</f>
+        <v>10.4</v>
       </c>
       <c r="F13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4)</f>
+        <v>10.4</v>
       </c>
       <c r="G13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4)</f>
+        <v>10.4</v>
       </c>
       <c r="H13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4)</f>
+        <v>10.4</v>
       </c>
       <c r="I13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4)</f>
+        <v>10.4</v>
       </c>
       <c r="J13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4)</f>
+        <v>10.4</v>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4)</f>
+        <v>10.4</v>
       </c>
       <c r="L13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4)</f>
+        <v>10.4</v>
       </c>
       <c r="M13" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4)</f>
+        <v>10.4</v>
       </c>
       <c r="N13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
@@ -1041,53 +1041,53 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46066.0)</f>
         <v>46066</v>
       </c>
-      <c r="B14" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),135.8)</f>
+        <v>135.8</v>
       </c>
       <c r="C14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.071111111111112)</f>
+        <v>12.07111111</v>
       </c>
       <c r="D14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.071111111111112)</f>
+        <v>12.07111111</v>
       </c>
       <c r="E14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.071111111111112)</f>
+        <v>12.07111111</v>
       </c>
       <c r="F14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.071111111111112)</f>
+        <v>12.07111111</v>
       </c>
       <c r="G14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.071111111111112)</f>
+        <v>12.07111111</v>
       </c>
       <c r="H14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.071111111111112)</f>
+        <v>12.07111111</v>
       </c>
       <c r="I14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.071111111111112)</f>
+        <v>12.07111111</v>
       </c>
       <c r="J14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.071111111111112)</f>
+        <v>12.07111111</v>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.071111111111112)</f>
+        <v>12.07111111</v>
       </c>
       <c r="L14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.071111111111112)</f>
+        <v>12.07111111</v>
       </c>
       <c r="M14" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.071111111111112)</f>
+        <v>12.07111111</v>
       </c>
       <c r="N14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1099,53 +1099,53 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46067.0)</f>
         <v>46067</v>
       </c>
-      <c r="B15" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),355.0)</f>
+        <v>355</v>
       </c>
       <c r="C15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.555555555555554)</f>
+        <v>31.55555556</v>
       </c>
       <c r="D15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.555555555555554)</f>
+        <v>31.55555556</v>
       </c>
       <c r="E15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.555555555555554)</f>
+        <v>31.55555556</v>
       </c>
       <c r="F15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.555555555555554)</f>
+        <v>31.55555556</v>
       </c>
       <c r="G15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.555555555555554)</f>
+        <v>31.55555556</v>
       </c>
       <c r="H15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.555555555555554)</f>
+        <v>31.55555556</v>
       </c>
       <c r="I15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.555555555555554)</f>
+        <v>31.55555556</v>
       </c>
       <c r="J15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.555555555555554)</f>
+        <v>31.55555556</v>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.555555555555554)</f>
+        <v>31.55555556</v>
       </c>
       <c r="L15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.555555555555554)</f>
+        <v>31.55555556</v>
       </c>
       <c r="M15" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.555555555555554)</f>
+        <v>31.55555556</v>
       </c>
       <c r="N15" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1157,53 +1157,53 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46068.0)</f>
         <v>46068</v>
       </c>
-      <c r="B16" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),259.7)</f>
+        <v>259.7</v>
       </c>
       <c r="C16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.084444444444443)</f>
+        <v>23.08444444</v>
       </c>
       <c r="D16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.084444444444443)</f>
+        <v>23.08444444</v>
       </c>
       <c r="E16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.084444444444443)</f>
+        <v>23.08444444</v>
       </c>
       <c r="F16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.084444444444443)</f>
+        <v>23.08444444</v>
       </c>
       <c r="G16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.084444444444443)</f>
+        <v>23.08444444</v>
       </c>
       <c r="H16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.084444444444443)</f>
+        <v>23.08444444</v>
       </c>
       <c r="I16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.084444444444443)</f>
+        <v>23.08444444</v>
       </c>
       <c r="J16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.084444444444443)</f>
+        <v>23.08444444</v>
       </c>
       <c r="K16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.084444444444443)</f>
+        <v>23.08444444</v>
       </c>
       <c r="L16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.084444444444443)</f>
+        <v>23.08444444</v>
       </c>
       <c r="M16" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.084444444444443)</f>
+        <v>23.08444444</v>
       </c>
       <c r="N16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1215,53 +1215,53 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46069.0)</f>
         <v>46069</v>
       </c>
-      <c r="B17" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186.4)</f>
+        <v>186.4</v>
       </c>
       <c r="C17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.56888888888889)</f>
+        <v>16.56888889</v>
       </c>
       <c r="D17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.56888888888889)</f>
+        <v>16.56888889</v>
       </c>
       <c r="E17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.56888888888889)</f>
+        <v>16.56888889</v>
       </c>
       <c r="F17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.56888888888889)</f>
+        <v>16.56888889</v>
       </c>
       <c r="G17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.56888888888889)</f>
+        <v>16.56888889</v>
       </c>
       <c r="H17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.56888888888889)</f>
+        <v>16.56888889</v>
       </c>
       <c r="I17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.56888888888889)</f>
+        <v>16.56888889</v>
       </c>
       <c r="J17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.56888888888889)</f>
+        <v>16.56888889</v>
       </c>
       <c r="K17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.56888888888889)</f>
+        <v>16.56888889</v>
       </c>
       <c r="L17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.56888888888889)</f>
+        <v>16.56888889</v>
       </c>
       <c r="M17" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.56888888888889)</f>
+        <v>16.56888889</v>
       </c>
       <c r="N17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1273,53 +1273,53 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46070.0)</f>
         <v>46070</v>
       </c>
-      <c r="B18" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),190.7)</f>
+        <v>190.7</v>
       </c>
       <c r="C18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.95111111111111)</f>
+        <v>16.95111111</v>
       </c>
       <c r="D18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.95111111111111)</f>
+        <v>16.95111111</v>
       </c>
       <c r="E18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.95111111111111)</f>
+        <v>16.95111111</v>
       </c>
       <c r="F18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.95111111111111)</f>
+        <v>16.95111111</v>
       </c>
       <c r="G18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.95111111111111)</f>
+        <v>16.95111111</v>
       </c>
       <c r="H18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.95111111111111)</f>
+        <v>16.95111111</v>
       </c>
       <c r="I18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.95111111111111)</f>
+        <v>16.95111111</v>
       </c>
       <c r="J18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.95111111111111)</f>
+        <v>16.95111111</v>
       </c>
       <c r="K18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.95111111111111)</f>
+        <v>16.95111111</v>
       </c>
       <c r="L18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.95111111111111)</f>
+        <v>16.95111111</v>
       </c>
       <c r="M18" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.95111111111111)</f>
+        <v>16.95111111</v>
       </c>
       <c r="N18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>

--- a/base_cinema_comissao.xlsx
+++ b/base_cinema_comissao.xlsx
@@ -1331,53 +1331,53 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46071.0)</f>
         <v>46071</v>
       </c>
-      <c r="B19" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146.6)</f>
+        <v>146.6</v>
       </c>
       <c r="C19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.03111111111111)</f>
+        <v>13.03111111</v>
       </c>
       <c r="D19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.03111111111111)</f>
+        <v>13.03111111</v>
       </c>
       <c r="E19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.03111111111111)</f>
+        <v>13.03111111</v>
       </c>
       <c r="F19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.03111111111111)</f>
+        <v>13.03111111</v>
       </c>
       <c r="G19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.03111111111111)</f>
+        <v>13.03111111</v>
       </c>
       <c r="H19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.03111111111111)</f>
+        <v>13.03111111</v>
       </c>
       <c r="I19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.03111111111111)</f>
+        <v>13.03111111</v>
       </c>
       <c r="J19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.03111111111111)</f>
+        <v>13.03111111</v>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.03111111111111)</f>
+        <v>13.03111111</v>
       </c>
       <c r="L19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.03111111111111)</f>
+        <v>13.03111111</v>
       </c>
       <c r="M19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.03111111111111)</f>
+        <v>13.03111111</v>
       </c>
       <c r="N19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
